--- a/backend/data/financials_by_company/0RY.F.xlsx
+++ b/backend/data/financials_by_company/0RY.F.xlsx
@@ -662,7 +662,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -671,107 +671,101 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-3607442</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-3047516</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-3047516</v>
-      </c>
+        <v>-6465104</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="H2" t="n">
-        <v>198660</v>
+        <v>146648</v>
       </c>
       <c r="I2" t="n">
-        <v>-6654958</v>
+        <v>-6465104</v>
       </c>
       <c r="J2" t="n">
-        <v>-6853618</v>
+        <v>-6611752</v>
       </c>
       <c r="K2" t="n">
-        <v>49139</v>
+        <v>12792</v>
       </c>
       <c r="L2" t="n">
-        <v>3143</v>
+        <v>396</v>
       </c>
       <c r="M2" t="n">
-        <v>52282</v>
+        <v>13973</v>
       </c>
       <c r="N2" t="n">
-        <v>-3809245</v>
+        <v>-6612148</v>
       </c>
       <c r="O2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="P2" t="n">
-        <v>228296917</v>
+        <v>189947806</v>
       </c>
       <c r="Q2" t="n">
-        <v>228296917</v>
+        <v>189947806</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.03</v>
+        <v>-0.034857</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.03</v>
+        <v>-0.034857</v>
       </c>
       <c r="T2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="U2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="V2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="W2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-6856761</v>
+        <v>-6612148</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1357372</v>
+        <v>1108507</v>
       </c>
       <c r="AA2" t="n">
-        <v>1690144</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-3047516</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3047516</v>
-      </c>
+        <v>1108507</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>49139</v>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+        <v>12792</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>785</v>
+      </c>
       <c r="AF2" t="n">
-        <v>3143</v>
+        <v>396</v>
       </c>
       <c r="AG2" t="n">
-        <v>52282</v>
+        <v>13973</v>
       </c>
       <c r="AH2" t="n">
-        <v>-5548528</v>
+        <v>-7733447</v>
       </c>
       <c r="AI2" t="n">
-        <v>5548528</v>
+        <v>7733447</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38817</v>
+        <v>3723</v>
       </c>
       <c r="AK2" t="n">
-        <v>198660</v>
+        <v>146648</v>
       </c>
       <c r="AL2" t="n">
-        <v>198660</v>
+        <v>146648</v>
       </c>
       <c r="AM2" t="n">
         <v>35971</v>
@@ -780,33 +774,33 @@
         <v>35971</v>
       </c>
       <c r="AO2" t="n">
-        <v>162689</v>
+        <v>110677</v>
       </c>
       <c r="AP2" t="n">
-        <v>2345560</v>
+        <v>4554750</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2965491</v>
+        <v>3028326</v>
       </c>
       <c r="AR2" t="n">
-        <v>115498</v>
+        <v>62821</v>
       </c>
       <c r="AS2" t="n">
-        <v>2849993</v>
+        <v>2965505</v>
       </c>
       <c r="AT2" t="n">
-        <v>1218452</v>
+        <v>730253</v>
       </c>
       <c r="AU2" t="n">
-        <v>41362</v>
+        <v>45479</v>
       </c>
       <c r="AV2" t="n">
-        <v>1590179</v>
+        <v>2189773</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -815,95 +809,95 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-11352292</v>
+        <v>-11144412</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="H3" t="n">
-        <v>189377</v>
+        <v>101480</v>
       </c>
       <c r="I3" t="n">
-        <v>-11352292</v>
+        <v>-11144412</v>
       </c>
       <c r="J3" t="n">
-        <v>-11541669</v>
+        <v>-11245892</v>
       </c>
       <c r="K3" t="n">
-        <v>228270</v>
+        <v>24965</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>228270</v>
+        <v>24965</v>
       </c>
       <c r="N3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="O3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="P3" t="n">
-        <v>221541718</v>
+        <v>214445142</v>
       </c>
       <c r="Q3" t="n">
-        <v>221541718</v>
+        <v>214445142</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.037105</v>
+        <v>-0.041021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.037105</v>
+        <v>-0.041021</v>
       </c>
       <c r="T3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="U3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="V3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="W3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-8217557</v>
+        <v>-8793521</v>
       </c>
       <c r="Z3" t="n">
-        <v>3095842</v>
+        <v>2427406</v>
       </c>
       <c r="AA3" t="n">
-        <v>3095842</v>
+        <v>2427406</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>228270</v>
+        <v>24965</v>
       </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>228270</v>
+        <v>24965</v>
       </c>
       <c r="AH3" t="n">
-        <v>-11541669</v>
+        <v>-11245892</v>
       </c>
       <c r="AI3" t="n">
-        <v>11541669</v>
+        <v>11245892</v>
       </c>
       <c r="AJ3" t="n">
-        <v>198847</v>
+        <v>90079</v>
       </c>
       <c r="AK3" t="n">
-        <v>189377</v>
+        <v>101480</v>
       </c>
       <c r="AL3" t="n">
-        <v>189377</v>
+        <v>101480</v>
       </c>
       <c r="AM3" t="n">
         <v>35971</v>
@@ -912,33 +906,33 @@
         <v>35971</v>
       </c>
       <c r="AO3" t="n">
-        <v>153406</v>
+        <v>65509</v>
       </c>
       <c r="AP3" t="n">
-        <v>3647711</v>
+        <v>5159179</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7505734</v>
+        <v>5895154</v>
       </c>
       <c r="AR3" t="n">
-        <v>175558</v>
+        <v>561860</v>
       </c>
       <c r="AS3" t="n">
-        <v>7330176</v>
+        <v>5333294</v>
       </c>
       <c r="AT3" t="n">
-        <v>992663</v>
+        <v>781248</v>
       </c>
       <c r="AU3" t="n">
-        <v>38609</v>
+        <v>99817</v>
       </c>
       <c r="AV3" t="n">
-        <v>6298904</v>
+        <v>4452229</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -947,95 +941,95 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-11144412</v>
+        <v>-11352292</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="H4" t="n">
-        <v>101480</v>
+        <v>189377</v>
       </c>
       <c r="I4" t="n">
-        <v>-11144412</v>
+        <v>-11352292</v>
       </c>
       <c r="J4" t="n">
-        <v>-11245892</v>
+        <v>-11541669</v>
       </c>
       <c r="K4" t="n">
-        <v>24965</v>
+        <v>228270</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>24965</v>
+        <v>228270</v>
       </c>
       <c r="N4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="O4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="P4" t="n">
-        <v>214445142</v>
+        <v>221541718</v>
       </c>
       <c r="Q4" t="n">
-        <v>214445142</v>
+        <v>221541718</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.041021</v>
+        <v>-0.037105</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.041021</v>
+        <v>-0.037105</v>
       </c>
       <c r="T4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="U4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="V4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="W4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-8793521</v>
+        <v>-8217557</v>
       </c>
       <c r="Z4" t="n">
-        <v>2427406</v>
+        <v>3095842</v>
       </c>
       <c r="AA4" t="n">
-        <v>2427406</v>
+        <v>3095842</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>24965</v>
+        <v>228270</v>
       </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>24965</v>
+        <v>228270</v>
       </c>
       <c r="AH4" t="n">
-        <v>-11245892</v>
+        <v>-11541669</v>
       </c>
       <c r="AI4" t="n">
-        <v>11245892</v>
+        <v>11541669</v>
       </c>
       <c r="AJ4" t="n">
-        <v>90079</v>
+        <v>198847</v>
       </c>
       <c r="AK4" t="n">
-        <v>101480</v>
+        <v>189377</v>
       </c>
       <c r="AL4" t="n">
-        <v>101480</v>
+        <v>189377</v>
       </c>
       <c r="AM4" t="n">
         <v>35971</v>
@@ -1044,33 +1038,33 @@
         <v>35971</v>
       </c>
       <c r="AO4" t="n">
-        <v>65509</v>
+        <v>153406</v>
       </c>
       <c r="AP4" t="n">
-        <v>5159179</v>
+        <v>3647711</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5895154</v>
+        <v>7505734</v>
       </c>
       <c r="AR4" t="n">
-        <v>561860</v>
+        <v>175558</v>
       </c>
       <c r="AS4" t="n">
-        <v>5333294</v>
+        <v>7330176</v>
       </c>
       <c r="AT4" t="n">
-        <v>781248</v>
+        <v>992663</v>
       </c>
       <c r="AU4" t="n">
-        <v>99817</v>
+        <v>38609</v>
       </c>
       <c r="AV4" t="n">
-        <v>4452229</v>
+        <v>6298904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1079,101 +1073,107 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-6465104</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>-3607442</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-3047516</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-3047516</v>
+      </c>
       <c r="G5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="H5" t="n">
-        <v>146648</v>
+        <v>198660</v>
       </c>
       <c r="I5" t="n">
-        <v>-6465104</v>
+        <v>-6654958</v>
       </c>
       <c r="J5" t="n">
-        <v>-6611752</v>
+        <v>-6853618</v>
       </c>
       <c r="K5" t="n">
-        <v>12792</v>
+        <v>49139</v>
       </c>
       <c r="L5" t="n">
-        <v>396</v>
+        <v>3143</v>
       </c>
       <c r="M5" t="n">
-        <v>13973</v>
+        <v>52282</v>
       </c>
       <c r="N5" t="n">
-        <v>-6612148</v>
+        <v>-3809245</v>
       </c>
       <c r="O5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="P5" t="n">
-        <v>189947806</v>
+        <v>228296917</v>
       </c>
       <c r="Q5" t="n">
-        <v>189947806</v>
+        <v>228296917</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.034857</v>
+        <v>-0.03</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.034857</v>
+        <v>-0.03</v>
       </c>
       <c r="T5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="U5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="V5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="W5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-6612148</v>
+        <v>-6856761</v>
       </c>
       <c r="Z5" t="n">
-        <v>1108507</v>
+        <v>-1357372</v>
       </c>
       <c r="AA5" t="n">
-        <v>1108507</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+        <v>1690144</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-3047516</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3047516</v>
+      </c>
       <c r="AD5" t="n">
-        <v>12792</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>785</v>
-      </c>
+        <v>49139</v>
+      </c>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>396</v>
+        <v>3143</v>
       </c>
       <c r="AG5" t="n">
-        <v>13973</v>
+        <v>52282</v>
       </c>
       <c r="AH5" t="n">
-        <v>-7733447</v>
+        <v>-5548528</v>
       </c>
       <c r="AI5" t="n">
-        <v>7733447</v>
+        <v>5548528</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3723</v>
+        <v>38817</v>
       </c>
       <c r="AK5" t="n">
-        <v>146648</v>
+        <v>198660</v>
       </c>
       <c r="AL5" t="n">
-        <v>146648</v>
+        <v>198660</v>
       </c>
       <c r="AM5" t="n">
         <v>35971</v>
@@ -1182,28 +1182,28 @@
         <v>35971</v>
       </c>
       <c r="AO5" t="n">
-        <v>110677</v>
+        <v>162689</v>
       </c>
       <c r="AP5" t="n">
-        <v>4554750</v>
+        <v>2345560</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3028326</v>
+        <v>2965491</v>
       </c>
       <c r="AR5" t="n">
-        <v>62821</v>
+        <v>115498</v>
       </c>
       <c r="AS5" t="n">
-        <v>2965505</v>
+        <v>2849993</v>
       </c>
       <c r="AT5" t="n">
-        <v>730253</v>
+        <v>1218452</v>
       </c>
       <c r="AU5" t="n">
-        <v>45479</v>
+        <v>41362</v>
       </c>
       <c r="AV5" t="n">
-        <v>2189773</v>
+        <v>1590179</v>
       </c>
     </row>
   </sheetData>
@@ -1479,600 +1479,600 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>248596750</v>
+        <v>207058329</v>
       </c>
       <c r="C2" t="n">
-        <v>248596750</v>
-      </c>
-      <c r="D2" t="n">
-        <v>163822</v>
-      </c>
+        <v>207058329</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>513064</v>
+        <v>1244789</v>
       </c>
       <c r="F2" t="n">
-        <v>867166</v>
+        <v>1706804</v>
       </c>
       <c r="G2" t="n">
-        <v>324826</v>
+        <v>1150675</v>
       </c>
       <c r="H2" t="n">
-        <v>513064</v>
-      </c>
-      <c r="I2" t="n">
-        <v>163822</v>
-      </c>
+        <v>1244789</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>867166</v>
+        <v>1706804</v>
       </c>
       <c r="K2" t="n">
-        <v>867166</v>
+        <v>1706804</v>
       </c>
       <c r="L2" t="n">
-        <v>867166</v>
+        <v>1706804</v>
       </c>
       <c r="M2" t="n">
-        <v>867166</v>
+        <v>1706804</v>
       </c>
       <c r="N2" t="n">
-        <v>5093243</v>
+        <v>531650</v>
       </c>
       <c r="O2" t="n">
-        <v>5093243</v>
+        <v>531650</v>
       </c>
       <c r="P2" t="n">
-        <v>-38674173</v>
+        <v>-14806334</v>
       </c>
       <c r="Q2" t="n">
-        <v>34448096</v>
+        <v>15981488</v>
       </c>
       <c r="R2" t="n">
-        <v>34448096</v>
+        <v>15981488</v>
       </c>
       <c r="S2" t="n">
-        <v>651542</v>
+        <v>1362970</v>
       </c>
       <c r="T2" t="n">
-        <v>89700</v>
+        <v>19686</v>
       </c>
       <c r="U2" t="n">
-        <v>4229</v>
+        <v>19686</v>
       </c>
       <c r="V2" t="n">
-        <v>4229</v>
-      </c>
-      <c r="W2" t="n">
-        <v>85471</v>
-      </c>
-      <c r="X2" t="n">
-        <v>85471</v>
-      </c>
+        <v>19686</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>561842</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>78351</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>78351</v>
-      </c>
+        <v>1343284</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>23782</v>
+        <v>137047</v>
       </c>
       <c r="AC2" t="n">
-        <v>459709</v>
+        <v>1206237</v>
       </c>
       <c r="AD2" t="n">
-        <v>459709</v>
+        <v>1206237</v>
       </c>
       <c r="AE2" t="n">
-        <v>248100</v>
+        <v>603074</v>
       </c>
       <c r="AF2" t="n">
-        <v>211609</v>
+        <v>603163</v>
       </c>
       <c r="AG2" t="n">
-        <v>1518708</v>
+        <v>3069774</v>
       </c>
       <c r="AH2" t="n">
-        <v>632040</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>575815</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-30</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>354102</v>
+        <v>462015</v>
       </c>
       <c r="AK2" t="n">
-        <v>354102</v>
+        <v>462015</v>
       </c>
       <c r="AL2" t="n">
-        <v>277938</v>
+        <v>113830</v>
       </c>
       <c r="AM2" t="n">
-        <v>-343467</v>
+        <v>-146822</v>
       </c>
       <c r="AN2" t="n">
-        <v>621405</v>
+        <v>260652</v>
       </c>
       <c r="AO2" t="n">
-        <v>164779</v>
+        <v>58356</v>
       </c>
       <c r="AP2" t="n">
-        <v>456626</v>
+        <v>202296</v>
       </c>
       <c r="AQ2" t="n">
-        <v>886668</v>
+        <v>2493959</v>
       </c>
       <c r="AR2" t="n">
-        <v>94973</v>
+        <v>56580</v>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>37199</v>
+        <v>163982</v>
       </c>
       <c r="AV2" t="n">
-        <v>37199</v>
+        <v>163982</v>
       </c>
       <c r="AW2" t="n">
-        <v>754496</v>
+        <v>2273397</v>
       </c>
       <c r="AX2" t="n">
         <v>45000</v>
       </c>
       <c r="AY2" t="n">
-        <v>709496</v>
+        <v>2228397</v>
       </c>
       <c r="AZ2" t="n">
-        <v>709496</v>
+        <v>2228397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>224502430</v>
+        <v>218669619</v>
       </c>
       <c r="C3" t="n">
-        <v>224502430</v>
+        <v>218669619</v>
       </c>
       <c r="D3" t="n">
+        <v>170140</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6946006</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7372050</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6838658</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6946006</v>
+      </c>
+      <c r="I3" t="n">
+        <v>170140</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7372050</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7372050</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7372050</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7372050</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3137326</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3137326</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-23599855</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>27834579</v>
+      </c>
+      <c r="R3" t="n">
+        <v>27834579</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1065719</v>
+      </c>
+      <c r="T3" t="n">
+        <v>133339</v>
+      </c>
+      <c r="U3" t="n">
+        <v>48733</v>
+      </c>
+      <c r="V3" t="n">
+        <v>48733</v>
+      </c>
+      <c r="W3" t="n">
         <v>84606</v>
       </c>
-      <c r="E3" t="n">
-        <v>5484378</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5874451</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5353357</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5484378</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="X3" t="n">
         <v>84606</v>
       </c>
-      <c r="J3" t="n">
-        <v>5874451</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5874451</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5874451</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5874451</v>
-      </c>
-      <c r="N3" t="n">
-        <v>6141261</v>
-      </c>
-      <c r="O3" t="n">
-        <v>6141261</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-31817412</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>31550602</v>
-      </c>
-      <c r="R3" t="n">
-        <v>31550602</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1820970</v>
-      </c>
-      <c r="T3" t="n">
-        <v>55382</v>
-      </c>
-      <c r="U3" t="n">
-        <v>55382</v>
-      </c>
-      <c r="V3" t="n">
-        <v>55382</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>1765588</v>
+        <v>932380</v>
       </c>
       <c r="Z3" t="n">
-        <v>84606</v>
+        <v>85534</v>
       </c>
       <c r="AA3" t="n">
-        <v>84606</v>
+        <v>85534</v>
       </c>
       <c r="AB3" t="n">
-        <v>158139</v>
+        <v>215909</v>
       </c>
       <c r="AC3" t="n">
-        <v>1522843</v>
+        <v>630937</v>
       </c>
       <c r="AD3" t="n">
-        <v>1522843</v>
+        <v>630937</v>
       </c>
       <c r="AE3" t="n">
-        <v>188937</v>
+        <v>352623</v>
       </c>
       <c r="AF3" t="n">
-        <v>1333906</v>
+        <v>278314</v>
       </c>
       <c r="AG3" t="n">
-        <v>7695421</v>
+        <v>8437769</v>
       </c>
       <c r="AH3" t="n">
-        <v>576476</v>
+        <v>666731</v>
       </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>390073</v>
+        <v>426044</v>
       </c>
       <c r="AK3" t="n">
-        <v>390073</v>
+        <v>426044</v>
       </c>
       <c r="AL3" t="n">
-        <v>186403</v>
+        <v>240687</v>
       </c>
       <c r="AM3" t="n">
-        <v>-269432</v>
+        <v>-204924</v>
       </c>
       <c r="AN3" t="n">
-        <v>455835</v>
+        <v>445611</v>
       </c>
       <c r="AO3" t="n">
-        <v>81490</v>
+        <v>170388</v>
       </c>
       <c r="AP3" t="n">
-        <v>374345</v>
+        <v>275223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7118945</v>
+        <v>7771038</v>
       </c>
       <c r="AR3" t="n">
-        <v>117569</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2766682</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2766682</v>
-      </c>
+        <v>93199</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
-        <v>65513</v>
+        <v>82415</v>
       </c>
       <c r="AV3" t="n">
-        <v>65513</v>
+        <v>82415</v>
       </c>
       <c r="AW3" t="n">
-        <v>4169181</v>
+        <v>7595424</v>
       </c>
       <c r="AX3" t="n">
         <v>45000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4124181</v>
+        <v>7550424</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4124181</v>
+        <v>7550424</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>218669619</v>
+        <v>224502430</v>
       </c>
       <c r="C4" t="n">
-        <v>218669619</v>
+        <v>224502430</v>
       </c>
       <c r="D4" t="n">
-        <v>170140</v>
+        <v>84606</v>
       </c>
       <c r="E4" t="n">
-        <v>6946006</v>
+        <v>5484378</v>
       </c>
       <c r="F4" t="n">
-        <v>7372050</v>
+        <v>5874451</v>
       </c>
       <c r="G4" t="n">
-        <v>6838658</v>
+        <v>5353357</v>
       </c>
       <c r="H4" t="n">
-        <v>6946006</v>
+        <v>5484378</v>
       </c>
       <c r="I4" t="n">
-        <v>170140</v>
+        <v>84606</v>
       </c>
       <c r="J4" t="n">
-        <v>7372050</v>
+        <v>5874451</v>
       </c>
       <c r="K4" t="n">
-        <v>7372050</v>
+        <v>5874451</v>
       </c>
       <c r="L4" t="n">
-        <v>7372050</v>
+        <v>5874451</v>
       </c>
       <c r="M4" t="n">
-        <v>7372050</v>
+        <v>5874451</v>
       </c>
       <c r="N4" t="n">
-        <v>3137326</v>
+        <v>6141261</v>
       </c>
       <c r="O4" t="n">
-        <v>3137326</v>
+        <v>6141261</v>
       </c>
       <c r="P4" t="n">
-        <v>-23599855</v>
+        <v>-31817412</v>
       </c>
       <c r="Q4" t="n">
-        <v>27834579</v>
+        <v>31550602</v>
       </c>
       <c r="R4" t="n">
-        <v>27834579</v>
+        <v>31550602</v>
       </c>
       <c r="S4" t="n">
-        <v>1065719</v>
+        <v>1820970</v>
       </c>
       <c r="T4" t="n">
-        <v>133339</v>
+        <v>55382</v>
       </c>
       <c r="U4" t="n">
-        <v>48733</v>
+        <v>55382</v>
       </c>
       <c r="V4" t="n">
-        <v>48733</v>
-      </c>
-      <c r="W4" t="n">
+        <v>55382</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="n">
+        <v>1765588</v>
+      </c>
+      <c r="Z4" t="n">
         <v>84606</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AA4" t="n">
         <v>84606</v>
       </c>
-      <c r="Y4" t="n">
-        <v>932380</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>85534</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>85534</v>
-      </c>
       <c r="AB4" t="n">
-        <v>215909</v>
+        <v>158139</v>
       </c>
       <c r="AC4" t="n">
-        <v>630937</v>
+        <v>1522843</v>
       </c>
       <c r="AD4" t="n">
-        <v>630937</v>
+        <v>1522843</v>
       </c>
       <c r="AE4" t="n">
-        <v>352623</v>
+        <v>188937</v>
       </c>
       <c r="AF4" t="n">
-        <v>278314</v>
+        <v>1333906</v>
       </c>
       <c r="AG4" t="n">
-        <v>8437769</v>
+        <v>7695421</v>
       </c>
       <c r="AH4" t="n">
-        <v>666731</v>
+        <v>576476</v>
       </c>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>426044</v>
+        <v>390073</v>
       </c>
       <c r="AK4" t="n">
-        <v>426044</v>
+        <v>390073</v>
       </c>
       <c r="AL4" t="n">
-        <v>240687</v>
+        <v>186403</v>
       </c>
       <c r="AM4" t="n">
-        <v>-204924</v>
+        <v>-269432</v>
       </c>
       <c r="AN4" t="n">
-        <v>445611</v>
+        <v>455835</v>
       </c>
       <c r="AO4" t="n">
-        <v>170388</v>
+        <v>81490</v>
       </c>
       <c r="AP4" t="n">
-        <v>275223</v>
+        <v>374345</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7771038</v>
+        <v>7118945</v>
       </c>
       <c r="AR4" t="n">
-        <v>93199</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>117569</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2766682</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2766682</v>
+      </c>
       <c r="AU4" t="n">
-        <v>82415</v>
+        <v>65513</v>
       </c>
       <c r="AV4" t="n">
-        <v>82415</v>
+        <v>65513</v>
       </c>
       <c r="AW4" t="n">
-        <v>7595424</v>
+        <v>4169181</v>
       </c>
       <c r="AX4" t="n">
         <v>45000</v>
       </c>
       <c r="AY4" t="n">
-        <v>7550424</v>
+        <v>4124181</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7550424</v>
+        <v>4124181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>207058329</v>
+        <v>248596750</v>
       </c>
       <c r="C5" t="n">
-        <v>207058329</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>248596750</v>
+      </c>
+      <c r="D5" t="n">
+        <v>163822</v>
+      </c>
       <c r="E5" t="n">
-        <v>1244789</v>
+        <v>513064</v>
       </c>
       <c r="F5" t="n">
-        <v>1706804</v>
+        <v>867166</v>
       </c>
       <c r="G5" t="n">
-        <v>1150675</v>
+        <v>324826</v>
       </c>
       <c r="H5" t="n">
-        <v>1244789</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>513064</v>
+      </c>
+      <c r="I5" t="n">
+        <v>163822</v>
+      </c>
       <c r="J5" t="n">
-        <v>1706804</v>
+        <v>867166</v>
       </c>
       <c r="K5" t="n">
-        <v>1706804</v>
+        <v>867166</v>
       </c>
       <c r="L5" t="n">
-        <v>1706804</v>
+        <v>867166</v>
       </c>
       <c r="M5" t="n">
-        <v>1706804</v>
+        <v>867166</v>
       </c>
       <c r="N5" t="n">
-        <v>531650</v>
+        <v>5093243</v>
       </c>
       <c r="O5" t="n">
-        <v>531650</v>
+        <v>5093243</v>
       </c>
       <c r="P5" t="n">
-        <v>-14806334</v>
+        <v>-38674173</v>
       </c>
       <c r="Q5" t="n">
-        <v>15981488</v>
+        <v>34448096</v>
       </c>
       <c r="R5" t="n">
-        <v>15981488</v>
+        <v>34448096</v>
       </c>
       <c r="S5" t="n">
-        <v>1362970</v>
+        <v>651542</v>
       </c>
       <c r="T5" t="n">
-        <v>19686</v>
+        <v>89700</v>
       </c>
       <c r="U5" t="n">
-        <v>19686</v>
+        <v>4229</v>
       </c>
       <c r="V5" t="n">
-        <v>19686</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+        <v>4229</v>
+      </c>
+      <c r="W5" t="n">
+        <v>85471</v>
+      </c>
+      <c r="X5" t="n">
+        <v>85471</v>
+      </c>
       <c r="Y5" t="n">
-        <v>1343284</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+        <v>561842</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>78351</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>78351</v>
+      </c>
       <c r="AB5" t="n">
-        <v>137047</v>
+        <v>23782</v>
       </c>
       <c r="AC5" t="n">
-        <v>1206237</v>
+        <v>459709</v>
       </c>
       <c r="AD5" t="n">
-        <v>1206237</v>
+        <v>459709</v>
       </c>
       <c r="AE5" t="n">
-        <v>603074</v>
+        <v>248100</v>
       </c>
       <c r="AF5" t="n">
-        <v>603163</v>
+        <v>211609</v>
       </c>
       <c r="AG5" t="n">
-        <v>3069774</v>
+        <v>1518708</v>
       </c>
       <c r="AH5" t="n">
-        <v>575815</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-30</v>
-      </c>
+        <v>632040</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>462015</v>
+        <v>354102</v>
       </c>
       <c r="AK5" t="n">
-        <v>462015</v>
+        <v>354102</v>
       </c>
       <c r="AL5" t="n">
-        <v>113830</v>
+        <v>277938</v>
       </c>
       <c r="AM5" t="n">
-        <v>-146822</v>
+        <v>-343467</v>
       </c>
       <c r="AN5" t="n">
-        <v>260652</v>
+        <v>621405</v>
       </c>
       <c r="AO5" t="n">
-        <v>58356</v>
+        <v>164779</v>
       </c>
       <c r="AP5" t="n">
-        <v>202296</v>
+        <v>456626</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2493959</v>
+        <v>886668</v>
       </c>
       <c r="AR5" t="n">
-        <v>56580</v>
+        <v>94973</v>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>163982</v>
+        <v>37199</v>
       </c>
       <c r="AV5" t="n">
-        <v>163982</v>
+        <v>37199</v>
       </c>
       <c r="AW5" t="n">
-        <v>2273397</v>
+        <v>754496</v>
       </c>
       <c r="AX5" t="n">
         <v>45000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2228397</v>
+        <v>709496</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2228397</v>
+        <v>709496</v>
       </c>
     </row>
   </sheetData>
@@ -2223,163 +2223,159 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-6219452</v>
+        <v>-5470757</v>
       </c>
       <c r="C2" t="n">
-        <v>-117922</v>
+        <v>-225121</v>
       </c>
       <c r="D2" t="n">
-        <v>3015416</v>
+        <v>6168754</v>
       </c>
       <c r="E2" t="n">
-        <v>-82281</v>
+        <v>-68271</v>
       </c>
       <c r="F2" t="n">
-        <v>3143</v>
+        <v>785</v>
       </c>
       <c r="G2" t="n">
-        <v>709496</v>
+        <v>2228397</v>
       </c>
       <c r="H2" t="n">
-        <v>4124181</v>
+        <v>1797958</v>
       </c>
       <c r="I2" t="n">
-        <v>-3414685</v>
+        <v>430439</v>
       </c>
       <c r="J2" t="n">
-        <v>2804767</v>
+        <v>5901196</v>
       </c>
       <c r="K2" t="n">
-        <v>2804767</v>
+        <v>5901196</v>
       </c>
       <c r="L2" t="n">
-        <v>-185454</v>
+        <v>-84874</v>
       </c>
       <c r="M2" t="n">
-        <v>2897494</v>
+        <v>5943633</v>
       </c>
       <c r="N2" t="n">
-        <v>-117922</v>
+        <v>-225121</v>
       </c>
       <c r="O2" t="n">
-        <v>3015416</v>
+        <v>6168754</v>
       </c>
       <c r="P2" t="n">
-        <v>-82281</v>
+        <v>-68271</v>
       </c>
       <c r="Q2" t="n">
-        <v>-82281</v>
+        <v>-68271</v>
       </c>
       <c r="R2" t="n">
-        <v>-82281</v>
+        <v>-68271</v>
       </c>
       <c r="S2" t="n">
-        <v>-82281</v>
+        <v>-68271</v>
       </c>
       <c r="T2" t="n">
-        <v>-6137171</v>
+        <v>-5402486</v>
       </c>
       <c r="U2" t="n">
-        <v>52282</v>
+        <v>20212</v>
       </c>
       <c r="V2" t="n">
-        <v>-3143</v>
+        <v>-785</v>
       </c>
       <c r="W2" t="n">
-        <v>-7876454</v>
+        <v>-6580420</v>
       </c>
       <c r="X2" t="n">
-        <v>-7876454</v>
+        <v>-6580420</v>
       </c>
       <c r="Y2" t="n">
-        <v>1690144</v>
+        <v>1158507</v>
       </c>
       <c r="Z2" t="n">
-        <v>1690144</v>
+        <v>1158507</v>
       </c>
       <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-7056732</v>
+        <v>-6523408</v>
       </c>
       <c r="C3" t="n">
-        <v>-24217</v>
+        <v>-467854</v>
       </c>
       <c r="D3" t="n">
-        <v>3740240</v>
+        <v>12320945</v>
       </c>
       <c r="E3" t="n">
-        <v>-99122</v>
-      </c>
-      <c r="F3" t="n">
-        <v>6557</v>
-      </c>
+        <v>-27006</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>4124181</v>
+        <v>7550424</v>
       </c>
       <c r="H3" t="n">
-        <v>7550424</v>
+        <v>2228397</v>
       </c>
       <c r="I3" t="n">
-        <v>-3426243</v>
+        <v>5322027</v>
       </c>
       <c r="J3" t="n">
-        <v>3630489</v>
+        <v>11845435</v>
       </c>
       <c r="K3" t="n">
-        <v>3630489</v>
+        <v>11845435</v>
       </c>
       <c r="L3" t="n">
-        <v>-171068</v>
+        <v>-15312</v>
       </c>
       <c r="M3" t="n">
-        <v>3716023</v>
+        <v>11853091</v>
       </c>
       <c r="N3" t="n">
-        <v>-24217</v>
+        <v>-467854</v>
       </c>
       <c r="O3" t="n">
-        <v>3740240</v>
+        <v>12320945</v>
       </c>
       <c r="P3" t="n">
-        <v>-99122</v>
+        <v>-27006</v>
       </c>
       <c r="Q3" t="n">
-        <v>-99122</v>
+        <v>-27006</v>
       </c>
       <c r="R3" t="n">
-        <v>-99122</v>
+        <v>-27006</v>
       </c>
       <c r="S3" t="n">
-        <v>-99122</v>
+        <v>-27006</v>
       </c>
       <c r="T3" t="n">
-        <v>-6957610</v>
+        <v>-6496402</v>
       </c>
       <c r="U3" t="n">
-        <v>228379</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-6557</v>
-      </c>
+        <v>25048</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-10275274</v>
+        <v>-8948856</v>
       </c>
       <c r="X3" t="n">
-        <v>-10275274</v>
+        <v>-8948856</v>
       </c>
       <c r="Y3" t="n">
-        <v>3095842</v>
+        <v>2427406</v>
       </c>
       <c r="Z3" t="n">
-        <v>3080842</v>
+        <v>2412406</v>
       </c>
       <c r="AA3" t="n">
         <v>15000</v>
@@ -2387,78 +2383,82 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-6523408</v>
+        <v>-7056732</v>
       </c>
       <c r="C4" t="n">
-        <v>-467854</v>
+        <v>-24217</v>
       </c>
       <c r="D4" t="n">
-        <v>12320945</v>
+        <v>3740240</v>
       </c>
       <c r="E4" t="n">
-        <v>-27006</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>-99122</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6557</v>
+      </c>
       <c r="G4" t="n">
+        <v>4124181</v>
+      </c>
+      <c r="H4" t="n">
         <v>7550424</v>
       </c>
-      <c r="H4" t="n">
-        <v>2228397</v>
-      </c>
       <c r="I4" t="n">
-        <v>5322027</v>
+        <v>-3426243</v>
       </c>
       <c r="J4" t="n">
-        <v>11845435</v>
+        <v>3630489</v>
       </c>
       <c r="K4" t="n">
-        <v>11845435</v>
+        <v>3630489</v>
       </c>
       <c r="L4" t="n">
-        <v>-15312</v>
+        <v>-171068</v>
       </c>
       <c r="M4" t="n">
-        <v>11853091</v>
+        <v>3716023</v>
       </c>
       <c r="N4" t="n">
-        <v>-467854</v>
+        <v>-24217</v>
       </c>
       <c r="O4" t="n">
-        <v>12320945</v>
+        <v>3740240</v>
       </c>
       <c r="P4" t="n">
-        <v>-27006</v>
+        <v>-99122</v>
       </c>
       <c r="Q4" t="n">
-        <v>-27006</v>
+        <v>-99122</v>
       </c>
       <c r="R4" t="n">
-        <v>-27006</v>
+        <v>-99122</v>
       </c>
       <c r="S4" t="n">
-        <v>-27006</v>
+        <v>-99122</v>
       </c>
       <c r="T4" t="n">
-        <v>-6496402</v>
+        <v>-6957610</v>
       </c>
       <c r="U4" t="n">
-        <v>25048</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>228379</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-6557</v>
+      </c>
       <c r="W4" t="n">
-        <v>-8948856</v>
+        <v>-10275274</v>
       </c>
       <c r="X4" t="n">
-        <v>-8948856</v>
+        <v>-10275274</v>
       </c>
       <c r="Y4" t="n">
-        <v>2427406</v>
+        <v>3095842</v>
       </c>
       <c r="Z4" t="n">
-        <v>2412406</v>
+        <v>3080842</v>
       </c>
       <c r="AA4" t="n">
         <v>15000</v>
@@ -2466,82 +2466,82 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-5470757</v>
+        <v>-6219452</v>
       </c>
       <c r="C5" t="n">
-        <v>-225121</v>
+        <v>-117922</v>
       </c>
       <c r="D5" t="n">
-        <v>6168754</v>
+        <v>3015416</v>
       </c>
       <c r="E5" t="n">
-        <v>-68271</v>
+        <v>-82281</v>
       </c>
       <c r="F5" t="n">
-        <v>785</v>
+        <v>3143</v>
       </c>
       <c r="G5" t="n">
-        <v>2228397</v>
+        <v>709496</v>
       </c>
       <c r="H5" t="n">
-        <v>1797958</v>
+        <v>4124181</v>
       </c>
       <c r="I5" t="n">
-        <v>430439</v>
+        <v>-3414685</v>
       </c>
       <c r="J5" t="n">
-        <v>5901196</v>
+        <v>2804767</v>
       </c>
       <c r="K5" t="n">
-        <v>5901196</v>
+        <v>2804767</v>
       </c>
       <c r="L5" t="n">
-        <v>-84874</v>
+        <v>-185454</v>
       </c>
       <c r="M5" t="n">
-        <v>5943633</v>
+        <v>2897494</v>
       </c>
       <c r="N5" t="n">
-        <v>-225121</v>
+        <v>-117922</v>
       </c>
       <c r="O5" t="n">
-        <v>6168754</v>
+        <v>3015416</v>
       </c>
       <c r="P5" t="n">
-        <v>-68271</v>
+        <v>-82281</v>
       </c>
       <c r="Q5" t="n">
-        <v>-68271</v>
+        <v>-82281</v>
       </c>
       <c r="R5" t="n">
-        <v>-68271</v>
+        <v>-82281</v>
       </c>
       <c r="S5" t="n">
-        <v>-68271</v>
+        <v>-82281</v>
       </c>
       <c r="T5" t="n">
-        <v>-5402486</v>
+        <v>-6137171</v>
       </c>
       <c r="U5" t="n">
-        <v>20212</v>
+        <v>52282</v>
       </c>
       <c r="V5" t="n">
-        <v>-785</v>
+        <v>-3143</v>
       </c>
       <c r="W5" t="n">
-        <v>-6580420</v>
+        <v>-7876454</v>
       </c>
       <c r="X5" t="n">
-        <v>-6580420</v>
+        <v>-7876454</v>
       </c>
       <c r="Y5" t="n">
-        <v>1158507</v>
+        <v>1690144</v>
       </c>
       <c r="Z5" t="n">
-        <v>1158507</v>
+        <v>1690144</v>
       </c>
       <c r="AA5" t="inlineStr"/>
     </row>
@@ -3052,187 +3052,187 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. David  Atkins M.B.A., Ph.D.', 'age': 60, 'title': 'CEO &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 295173, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. David  Atkins M.B.A., Ph.D.', 'age': 60, 'title': 'CEO &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 292545, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -3342,34 +3342,34 @@
         <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0615</v>
+        <v>0.064</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0615</v>
+        <v>0.064</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.481</v>
+        <v>0.446</v>
       </c>
       <c r="AF2" t="n">
         <v>700</v>
@@ -3387,16 +3387,16 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AL2" t="n">
         <v>0.0645</v>
       </c>
-      <c r="AL2" t="n">
-        <v>0.07149999999999999</v>
-      </c>
       <c r="AM2" t="n">
-        <v>22824410</v>
+        <v>20524276</v>
       </c>
       <c r="AN2" t="n">
-        <v>22902236</v>
+        <v>23822684</v>
       </c>
       <c r="AO2" t="n">
         <v>0.027</v>
@@ -3411,13 +3411,13 @@
         <v>0.027</v>
       </c>
       <c r="AS2" t="n">
-        <v>13.851671</v>
+        <v>12.455767</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.09207</v>
+        <v>0.07974000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0756525</v>
+        <v>0.076845</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20271372</v>
+        <v>18080798</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -3455,10 +3455,10 @@
         <v>353866857</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0036982829</v>
+        <v>0.0036645455</v>
       </c>
       <c r="BH2" t="n">
-        <v>17.440525</v>
+        <v>15.827337</v>
       </c>
       <c r="BI2" t="n">
         <v>1751241600</v>
@@ -3476,16 +3476,16 @@
         <v>-0.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>12.302</v>
+        <v>10.973</v>
       </c>
       <c r="BO2" t="n">
-        <v>-3.168</v>
+        <v>-2.825</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.8636364</v>
+        <v>1</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.0645</v>
+        <v>0.058</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -3592,140 +3592,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CU2" t="n">
-        <v>0.0645</v>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>Rhythm Biosciences Ltd        R</t>
+        </is>
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>Rhythm Biosciences Ltd        R</t>
-        </is>
-      </c>
-      <c r="CW2" t="inlineStr">
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>-0.0060000047</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>0.058 - 0.058</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>0.030999998</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.1481481</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>0.027 - 0.144</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.085999995</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.5972222</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>100</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1756378740</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>1756728000</v>
+      </c>
+      <c r="DI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.021740004</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.27263612</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.018845</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.24523391</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1676962800000</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-9.375007</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>Rhythm Biosciences Limited</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>1780406702</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DX2" t="n">
+        <v>1782134701</v>
+      </c>
+      <c r="DY2" t="inlineStr">
         <is>
           <t>FRA</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>finmb_540780120</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Europe/Berlin</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>CEST</t>
         </is>
       </c>
-      <c r="DD2" t="n">
+      <c r="EC2" t="n">
         <v>7200000</v>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>dr_market</t>
         </is>
       </c>
-      <c r="DF2" t="b">
+      <c r="EE2" t="b">
         <v>0</v>
-      </c>
-      <c r="DG2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-0.027570002</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.2994461</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>-0.011152506</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.14741755</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1676962800000</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.002999995</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>0.0645 - 0.0645</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>11</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.037499994</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1.3888886</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>0.027 - 0.144</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.0795</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.5520833000000001</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>86.36364</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1756378740</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1756728000</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>4.8780403</v>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
